--- a/test-cases/Zawaaj_Tests_SuperAdmin.xlsx
+++ b/test-cases/Zawaaj_Tests_SuperAdmin.xlsx
@@ -6,6 +6,7 @@
     <sheet name="1. Parent Registration Path A" sheetId="1" r:id="rId1"/>
     <sheet name="2. Invite Tokens" sheetId="2" r:id="rId2"/>
     <sheet name="3. Events Management" sheetId="3" r:id="rId3"/>
+    <sheet name="4. Admin Accounts" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -402,13 +403,13 @@
   <dimension ref="A1:K12"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="38.83203125" customWidth="1"/>
-    <col min="6" max="6" width="32.83203125" customWidth="1"/>
-    <col min="7" max="7" width="48.83203125" customWidth="1"/>
-    <col min="8" max="8" width="48.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="40.83203125" customWidth="1"/>
+    <col min="6" max="6" width="34.83203125" customWidth="1"/>
+    <col min="7" max="7" width="50.83203125" customWidth="1"/>
+    <col min="8" max="8" width="50.83203125" customWidth="1"/>
     <col min="9" max="9" width="30.83203125" customWidth="1"/>
     <col min="10" max="10" width="12.83203125" customWidth="1"/>
     <col min="11" max="11" width="24.83203125" customWidth="1"/>
@@ -454,7 +455,7 @@
         <v>PAR-A-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Self</v>
+        <v>Super Admin</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -469,7 +470,7 @@
         <v>No existing account with email</v>
       </c>
       <c r="G2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Go to /register
+        <v xml:space="preserve">1. Go to /register/parent
 2. Enter email
 3. Click Next</v>
       </c>
@@ -491,7 +492,7 @@
         <v>PAR-A-002</v>
       </c>
       <c r="B3" t="str">
-        <v>Self</v>
+        <v>Super Admin</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -506,7 +507,7 @@
         <v>Email exists in auth.users</v>
       </c>
       <c r="G3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Go to /register
+        <v xml:space="preserve">1. Go to /register/parent
 2. Enter existing email
 3. Click Next</v>
       </c>
@@ -523,12 +524,12 @@
         <v/>
       </c>
     </row>
-    <row r="4">
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
         <v>PAR-A-003</v>
       </c>
       <c r="B4" t="str">
-        <v>Self</v>
+        <v>Super Admin</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -537,16 +538,17 @@
         <v>Registration</v>
       </c>
       <c r="E4" t="str">
-        <v>Complete 8-step registration wizard — candidate details</v>
+        <v>Contact details step</v>
       </c>
       <c r="F4" t="str">
-        <v>Valid email; no existing account</v>
-      </c>
-      <c r="G4" t="str">
-        <v>1. Complete steps 1-3: candidate personal info (name, DOB, location, profession, education, faith, bio)</v>
+        <v>Valid email entered; on step 1</v>
+      </c>
+      <c r="G4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Complete contact details: full name, relationship, phone, email
+2. Click Next</v>
       </c>
       <c r="H4" t="str">
-        <v>Form validates each step before allowing Next</v>
+        <v>All fields required; cannot proceed without completing them</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -563,7 +565,7 @@
         <v>PAR-A-004</v>
       </c>
       <c r="B5" t="str">
-        <v>Self</v>
+        <v>Super Admin</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -572,16 +574,16 @@
         <v>Registration</v>
       </c>
       <c r="E5" t="str">
-        <v>Guardian / contact details step (step 4)</v>
+        <v>Male guardian triggers female contact step</v>
       </c>
       <c r="F5" t="str">
-        <v>No invite token; continuing registration</v>
+        <v>On step 1; selected Father or Male guardian as relationship</v>
       </c>
       <c r="G5" t="str">
-        <v>1. Complete step 4: guardian name, contact number, relationship</v>
+        <v>1. Click Next after entering male guardian details</v>
       </c>
       <c r="H5" t="str">
-        <v>Guardian fields required; cannot skip</v>
+        <v>Extra step appears asking for female family contact or reason for absence</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -593,12 +595,12 @@
         <v/>
       </c>
     </row>
-    <row r="6">
+    <row r="6" xml:space="preserve">
       <c r="A6" t="str">
         <v>PAR-A-005</v>
       </c>
       <c r="B6" t="str">
-        <v>Self</v>
+        <v>Super Admin + Member</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -607,16 +609,18 @@
         <v>Registration</v>
       </c>
       <c r="E6" t="str">
-        <v>Preferences step</v>
+        <v>Form state preserved if user opens T&amp;C mid-wizard</v>
       </c>
       <c r="F6" t="str">
-        <v>On step 5</v>
-      </c>
-      <c r="G6" t="str">
-        <v>1. Complete partner preferences (age range, location, school of thought, ethnicity)</v>
+        <v>In the middle of completing the wizard (e.g. step 2 filled in)</v>
+      </c>
+      <c r="G6" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Fill in steps 1–2 of the registration form
+2. Click the Terms of Use link (opens in a new tab)
+3. Close the T&amp;C tab and return to the registration form</v>
       </c>
       <c r="H6" t="str">
-        <v>All fields optional; can proceed without selecting</v>
+        <v>All previously entered fields are still filled in — the form has not been cleared</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -633,7 +637,7 @@
         <v>PAR-A-006</v>
       </c>
       <c r="B7" t="str">
-        <v>Self</v>
+        <v>Super Admin</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -642,17 +646,17 @@
         <v>Registration</v>
       </c>
       <c r="E7" t="str">
-        <v>Terms &amp; consent step</v>
+        <v>Terms &amp; confirmation step</v>
       </c>
       <c r="F7" t="str">
-        <v>On step 7</v>
+        <v>On final step</v>
       </c>
       <c r="G7" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Check consent and terms boxes
-2. Click Submit</v>
+        <v xml:space="preserve">1. Check both consent boxes
+2. Click Create account</v>
       </c>
       <c r="H7" t="str">
-        <v>Cannot submit without both boxes checked</v>
+        <v>Cannot submit without both boxes ticked</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -669,7 +673,7 @@
         <v>PAR-A-007</v>
       </c>
       <c r="B8" t="str">
-        <v>Self</v>
+        <v>Super Admin</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -684,10 +688,10 @@
         <v>All steps complete; valid data</v>
       </c>
       <c r="G8" t="str">
-        <v>1. Click Submit on final step</v>
+        <v>1. Click Create account on final step</v>
       </c>
       <c r="H8" t="str">
-        <v>Account created; family account created; profile created with status=pending; redirect to /pending</v>
+        <v>Email verification screen shown; auth user created; family account created with status=active; profile created with status=pending</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -704,7 +708,7 @@
         <v>PAR-A-008</v>
       </c>
       <c r="B9" t="str">
-        <v>Self</v>
+        <v>Super Admin</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -713,16 +717,16 @@
         <v>Post-registration</v>
       </c>
       <c r="E9" t="str">
-        <v>Pending page after registration</v>
+        <v>Email verification screen after registration</v>
       </c>
       <c r="F9" t="str">
         <v>Just completed registration</v>
       </c>
       <c r="G9" t="str">
-        <v>1. After redirect to /pending</v>
+        <v>1. Review the screen shown after clicking Create account</v>
       </c>
       <c r="H9" t="str">
-        <v>Clock icon shown; "Application submitted — JazakAllahu Khayran" message; sign-out link</v>
+        <v>Envelope illustration shown; registered email address displayed; "Resend email" button available</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -754,11 +758,11 @@
         <v>Profile status = pending</v>
       </c>
       <c r="G10" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Sign in as another member
+        <v xml:space="preserve">1. Sign in as another approved member
 2. Browse member directory</v>
       </c>
       <c r="H10" t="str">
-        <v>Newly registered profile not visible</v>
+        <v>Newly registered profile not visible in browse</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -770,7 +774,7 @@
         <v/>
       </c>
     </row>
-    <row r="11">
+    <row r="11" xml:space="preserve">
       <c r="A11" t="str">
         <v>PAR-A-010</v>
       </c>
@@ -784,16 +788,18 @@
         <v>Family account</v>
       </c>
       <c r="E11" t="str">
-        <v>Family account created on registration</v>
+        <v>Family account created and active after email verification</v>
       </c>
       <c r="F11" t="str">
-        <v>Completed Path A registration</v>
-      </c>
-      <c r="G11" t="str">
-        <v>1. In Supabase / admin families view, search by contact email</v>
+        <v>Registration completed and email verified</v>
+      </c>
+      <c r="G11" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Sign in as super_admin
+2. Go to /admin/accounts
+3. Search by contact email</v>
       </c>
       <c r="H11" t="str">
-        <v>Family account row exists with contact_full_name, contact_email, registration_path = direct</v>
+        <v>Family account row exists with status = Active; no manual approval required</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -819,17 +825,17 @@
         <v>Family account</v>
       </c>
       <c r="E12" t="str">
-        <v>Admin can view family details after Path A</v>
+        <v>Candidate profile visible under family account</v>
       </c>
       <c r="F12" t="str">
-        <v>As admin; on /admin/families</v>
+        <v>As super_admin; on /admin/accounts</v>
       </c>
       <c r="G12" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Search for family
-2. Open family row</v>
+        <v xml:space="preserve">1. Search for the family
+2. Click the candidates count to expand the row</v>
       </c>
       <c r="H12" t="str">
-        <v>Contact details, family members, invite tokens all visible</v>
+        <v>Candidate profile shown with status = Pending Review; Approve and Reject buttons visible</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -850,16 +856,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K13"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="38.83203125" customWidth="1"/>
-    <col min="6" max="6" width="32.83203125" customWidth="1"/>
-    <col min="7" max="7" width="48.83203125" customWidth="1"/>
-    <col min="8" max="8" width="48.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="40.83203125" customWidth="1"/>
+    <col min="6" max="6" width="34.83203125" customWidth="1"/>
+    <col min="7" max="7" width="50.83203125" customWidth="1"/>
+    <col min="8" max="8" width="50.83203125" customWidth="1"/>
     <col min="9" max="9" width="30.83203125" customWidth="1"/>
     <col min="10" max="10" width="12.83203125" customWidth="1"/>
     <col min="11" max="11" width="24.83203125" customWidth="1"/>
@@ -917,7 +923,7 @@
         <v>Admin generates child_invite token</v>
       </c>
       <c r="F2" t="str">
-        <v>Signed in as super_admin; on /admin/families</v>
+        <v>Signed in as super_admin; on /admin/accounts or /admin/families</v>
       </c>
       <c r="G2" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Find a family account
@@ -1174,7 +1180,7 @@
 2. Observe step count</v>
       </c>
       <c r="H9" t="str">
-        <v>Guardian details step (step 4) not shown; EFFECTIVE_TOTAL = 7 steps total</v>
+        <v>Guardian details step (step 4) not shown; effective total is one step fewer</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -1245,7 +1251,7 @@
 2. Submit</v>
       </c>
       <c r="H11" t="str">
-        <v>New profile created; family_account_id set to existing family account; NO new family account created</v>
+        <v>New profile created; family_account_id set to existing family account; no new family account created</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -1313,11 +1319,12 @@
         <v>Registration completed via invite token</v>
       </c>
       <c r="G13" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Go to /admin/families
-2. Open the family account that issued the token</v>
+        <v xml:space="preserve">1. Go to /admin/accounts
+2. Find the family account that issued the token
+3. Click candidates count to expand</v>
       </c>
       <c r="H13" t="str">
-        <v>New member profile appears under family account members list</v>
+        <v>New candidate profile appears with status = Pending Review</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -1326,117 +1333,12 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>INV-013</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Super Admin</v>
-      </c>
-      <c r="C14" t="str">
-        <v/>
-      </c>
-      <c r="D14" t="str">
-        <v>Admin — families view</v>
-      </c>
-      <c r="E14" t="str">
-        <v>Families page lists all family accounts</v>
-      </c>
-      <c r="F14" t="str">
-        <v>Signed in as super_admin</v>
-      </c>
-      <c r="G14" t="str">
-        <v>1. Navigate to /admin/families</v>
-      </c>
-      <c r="H14" t="str">
-        <v>All family accounts listed with contact info, member count, registration path</v>
-      </c>
-      <c r="I14" t="str">
-        <v/>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>INV-014</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Super Admin</v>
-      </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <v>Admin — families view</v>
-      </c>
-      <c r="E15" t="str">
-        <v>Filter families by registration path</v>
-      </c>
-      <c r="F15" t="str">
-        <v>On /admin/families</v>
-      </c>
-      <c r="G15" t="str">
-        <v>1. Apply filter for "direct" or "child_direct"</v>
-      </c>
-      <c r="H15" t="str">
-        <v>List updates to show only matching families</v>
-      </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>INV-015</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Super Admin</v>
-      </c>
-      <c r="C16" t="str">
-        <v/>
-      </c>
-      <c r="D16" t="str">
-        <v>Admin — families view</v>
-      </c>
-      <c r="E16" t="str">
-        <v>Search families by name or email</v>
-      </c>
-      <c r="F16" t="str">
-        <v>On /admin/families</v>
-      </c>
-      <c r="G16" t="str">
-        <v>1. Type in search box</v>
-      </c>
-      <c r="H16" t="str">
-        <v>Results filter to matching families</v>
-      </c>
-      <c r="I16" t="str">
-        <v/>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1446,13 +1348,13 @@
   <dimension ref="A1:K13"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="38.83203125" customWidth="1"/>
-    <col min="6" max="6" width="32.83203125" customWidth="1"/>
-    <col min="7" max="7" width="48.83203125" customWidth="1"/>
-    <col min="8" max="8" width="48.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="40.83203125" customWidth="1"/>
+    <col min="6" max="6" width="34.83203125" customWidth="1"/>
+    <col min="7" max="7" width="50.83203125" customWidth="1"/>
+    <col min="8" max="8" width="50.83203125" customWidth="1"/>
     <col min="9" max="9" width="30.83203125" customWidth="1"/>
     <col min="10" max="10" width="12.83203125" customWidth="1"/>
     <col min="11" max="11" width="24.83203125" customWidth="1"/>
@@ -1840,7 +1742,7 @@
         <v>Member sees upcoming events</v>
       </c>
       <c r="F11" t="str">
-        <v>Upcoming event exists with show_in_history or status=upcoming</v>
+        <v>Upcoming event exists</v>
       </c>
       <c r="G11" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Sign in as member
@@ -1935,4 +1837,742 @@
     <ignoredError numberStoredAsText="1" sqref="A1:K13"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K20"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="40.83203125" customWidth="1"/>
+    <col min="6" max="6" width="34.83203125" customWidth="1"/>
+    <col min="7" max="7" width="50.83203125" customWidth="1"/>
+    <col min="8" max="8" width="50.83203125" customWidth="1"/>
+    <col min="9" max="9" width="30.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="24.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Test ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Who's needed</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Tester</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Test Case</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Pre-conditions</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Steps</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Expected Behaviour</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Actual Behaviour</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Pass / Fail</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ACC-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v>Accounts page</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Access /admin/accounts from sidebar</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Signed in as super_admin</v>
+      </c>
+      <c r="G2" t="str">
+        <v>1. Click "Accounts" in the admin sidebar (under Dashboard section)</v>
+      </c>
+      <c r="H2" t="str">
+        <v>/admin/accounts loads; table shows all family accounts with columns: Contact, Plan, Status, Candidates, Last Active, Registered</v>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ACC-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Manager</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v>Accounts page</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Accounts not accessible to managers</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Signed in as manager</v>
+      </c>
+      <c r="G3" t="str">
+        <v>1. Try to navigate to /admin/accounts</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Redirected away (403 or to /admin/introductions); Accounts not visible in sidebar</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>ACC-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>Status badges</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Active account shows green "Active" badge</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Family account with status = active</v>
+      </c>
+      <c r="G4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. On /admin/accounts
+2. Locate an account that has verified their email</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Green "Active" badge in the Status column</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>ACC-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v>Status badges</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Unverified account shows blue "Invited" badge</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Family account with status = pending_email_verification</v>
+      </c>
+      <c r="G5" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. On /admin/accounts
+2. Locate a newly registered account that has not verified email yet</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Blue "Invited" badge in the Status column</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>ACC-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v>Status badges</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Suspended account shows grey "Inactive" badge</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Family account with status = suspended</v>
+      </c>
+      <c r="G6" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. On /admin/accounts
+2. Locate a suspended account</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Grey "Inactive" badge in the Status column</v>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>ACC-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>Candidates</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Expand candidates row</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Family account with at least one candidate profile</v>
+      </c>
+      <c r="G7" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. On /admin/accounts
+2. Click the candidates count button on a family row</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Candidate sub-rows appear showing: initials avatar, name, gender, age, location, status badge, and action buttons</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str">
+        <v>ACC-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v>Candidates</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Pending badge on candidates button when review needed</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Family account has a candidate profile with status = pending</v>
+      </c>
+      <c r="G8" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. On /admin/accounts
+2. Look at the candidates count button for that family</v>
+      </c>
+      <c r="H8" t="str">
+        <v>An amber number badge appears on the button showing the count of pending-review profiles; those families start expanded automatically</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str">
+        <v>ACC-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v>Candidates</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Approve a pending candidate profile inline</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Candidate profile with status = Pending Review visible in expanded row</v>
+      </c>
+      <c r="G9" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Expand the family's candidate rows
+2. Click "Approve" next to the pending candidate</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Status badge changes to "Approved" immediately; Approve button replaced with Pause button</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str">
+        <v>ACC-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v>Candidates</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Reject a pending candidate profile inline</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Candidate profile with status = Pending Review</v>
+      </c>
+      <c r="G10" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Expand the family's candidate rows
+2. Click "Reject"</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Status badge changes to "Rejected"; Approve button appears for future reinstatement</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11" t="str">
+        <v>ACC-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v>Candidates</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Pause an approved candidate profile inline</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Candidate profile with status = Approved</v>
+      </c>
+      <c r="G11" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Expand the family's candidate rows
+2. Click "Pause"</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Status badge changes to "Paused"; profile disappears from member browse</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
+        <v>ACC-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v>Candidates</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Re-approve a paused or rejected profile inline</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Candidate profile with status = Paused or Rejected</v>
+      </c>
+      <c r="G12" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Expand the family's candidate rows
+2. Click "Approve"</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Status badge changes to "Approved"; profile reappears in member browse</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>ACC-012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v>Candidates</v>
+      </c>
+      <c r="E13" t="str">
+        <v>View full profile from accounts page</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Candidate row visible in expanded accounts view</v>
+      </c>
+      <c r="G13" t="str">
+        <v>1. Click "View" next to any candidate</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Navigates to /admin/profile/[id] — full admin profile view with all sensitive fields</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str">
+        <v>ACC-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v>Last Active</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Last active column shows relative time for signed-in users</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Family account where the guardian has signed in before</v>
+      </c>
+      <c r="G14" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. On /admin/accounts
+2. Look at the Last Active column for an active account</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Relative time shown (e.g. "3d ago", "2h ago")</v>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str">
+        <v>ACC-014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>Last Active</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Last active shows dash for unverified accounts</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Family account that has never signed in (status = Invited)</v>
+      </c>
+      <c r="G15" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. On /admin/accounts
+2. Look at Last Active column for an Invited account</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Dash (—) shown in Last Active column</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str">
+        <v>ACC-015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v>Delete account</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Delete a family account with confirmation</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Family account exists on /admin/accounts</v>
+      </c>
+      <c r="G16" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Click the bin/delete icon on a family row
+2. Read the confirmation prompt
+3. Click OK</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Account disappears from the list; family account, linked profiles, and auth users all removed</v>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>ACC-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v>Delete account</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Cancel delete shows no change</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Family account exists on /admin/accounts</v>
+      </c>
+      <c r="G17" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Click the bin/delete icon on a family row
+2. Click Cancel on the confirmation prompt</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Nothing changes; account remains in the list</v>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>ACC-017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v>Search &amp; filter</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Search by contact name</v>
+      </c>
+      <c r="F18" t="str">
+        <v>On /admin/accounts</v>
+      </c>
+      <c r="G18" t="str">
+        <v>1. Type a guardian's name in the search box</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Only accounts with matching contact name appear; case-insensitive</v>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>ACC-018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v>Search &amp; filter</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Search by email address</v>
+      </c>
+      <c r="F19" t="str">
+        <v>On /admin/accounts</v>
+      </c>
+      <c r="G19" t="str">
+        <v>1. Type part of an email address in the search box</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Only accounts with matching contact email appear</v>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>ACC-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v>Search &amp; filter</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Status tab counts are accurate</v>
+      </c>
+      <c r="F20" t="str">
+        <v>On /admin/accounts with a mix of Active, Invited, and Inactive accounts</v>
+      </c>
+      <c r="G20" t="str">
+        <v>1. Note the count shown in each tab label</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Active, Invited, and Inactive counts add up to the total shown in the All tab</v>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K20"/>
+  </ignoredErrors>
+</worksheet>
 </file>